--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1081,6 +1081,357 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>123872155</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571504</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7050910</v>
+      </c>
+      <c r="S6" t="n">
+        <v>18</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>123871751</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Prästback, Prästback, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571473</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7050855</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:55</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>123871902</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57506</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Prästback, Prästback, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571488</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7050864</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-08</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123872155</v>
+        <v>123871902</v>
       </c>
       <c r="B6" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,22 +1119,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571504</v>
+        <v>571488</v>
       </c>
       <c r="R6" t="n">
-        <v>7050910</v>
+        <v>7050864</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,10 +1200,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123871751</v>
+        <v>123872155</v>
       </c>
       <c r="B7" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1236,22 +1236,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571473</v>
+        <v>571504</v>
       </c>
       <c r="R7" t="n">
-        <v>7050855</v>
+        <v>7050910</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,10 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123871902</v>
+        <v>123871751</v>
       </c>
       <c r="B8" t="n">
-        <v>57506</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1353,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571488</v>
+        <v>571473</v>
       </c>
       <c r="R8" t="n">
-        <v>7050864</v>
+        <v>7050855</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123871902</v>
+        <v>123872155</v>
       </c>
       <c r="B6" t="n">
         <v>57507</v>
@@ -1119,22 +1119,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571488</v>
+        <v>571504</v>
       </c>
       <c r="R6" t="n">
-        <v>7050864</v>
+        <v>7050910</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123872155</v>
+        <v>123871902</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1236,22 +1236,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571504</v>
+        <v>571488</v>
       </c>
       <c r="R7" t="n">
-        <v>7050910</v>
+        <v>7050864</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123872155</v>
+        <v>123871751</v>
       </c>
       <c r="B6" t="n">
         <v>57507</v>
@@ -1119,22 +1119,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571504</v>
+        <v>571473</v>
       </c>
       <c r="R6" t="n">
-        <v>7050910</v>
+        <v>7050855</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123871902</v>
+        <v>123872155</v>
       </c>
       <c r="B7" t="n">
         <v>57507</v>
@@ -1236,22 +1236,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571488</v>
+        <v>571504</v>
       </c>
       <c r="R7" t="n">
-        <v>7050864</v>
+        <v>7050910</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123871751</v>
+        <v>123871902</v>
       </c>
       <c r="B8" t="n">
         <v>57507</v>
@@ -1353,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571473</v>
+        <v>571488</v>
       </c>
       <c r="R8" t="n">
-        <v>7050855</v>
+        <v>7050864</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123871751</v>
+        <v>123871902</v>
       </c>
       <c r="B6" t="n">
         <v>57507</v>
@@ -1119,7 +1119,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571473</v>
+        <v>571488</v>
       </c>
       <c r="R6" t="n">
-        <v>7050855</v>
+        <v>7050864</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123871902</v>
+        <v>123871751</v>
       </c>
       <c r="B8" t="n">
         <v>57507</v>
@@ -1353,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571488</v>
+        <v>571473</v>
       </c>
       <c r="R8" t="n">
-        <v>7050864</v>
+        <v>7050855</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123872155</v>
+        <v>123871751</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1119,22 +1119,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571504</v>
+        <v>571473</v>
       </c>
       <c r="R6" t="n">
-        <v>7050910</v>
+        <v>7050855</v>
       </c>
       <c r="S6" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123871751</v>
+        <v>123872155</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1353,22 +1353,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571473</v>
+        <v>571504</v>
       </c>
       <c r="R8" t="n">
-        <v>7050855</v>
+        <v>7050910</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123871751</v>
+        <v>123871902</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1119,7 +1119,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571473</v>
+        <v>571488</v>
       </c>
       <c r="R6" t="n">
-        <v>7050855</v>
+        <v>7050864</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123871902</v>
+        <v>123871751</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1236,7 +1236,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571488</v>
+        <v>571473</v>
       </c>
       <c r="R7" t="n">
-        <v>7050864</v>
+        <v>7050855</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123871902</v>
+        <v>123871751</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1119,7 +1119,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1128,13 +1128,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571488</v>
+        <v>571473</v>
       </c>
       <c r="R6" t="n">
-        <v>7050864</v>
+        <v>7050855</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123871751</v>
+        <v>123872155</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1236,22 +1236,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571473</v>
+        <v>571504</v>
       </c>
       <c r="R7" t="n">
-        <v>7050855</v>
+        <v>7050910</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123872155</v>
+        <v>123871902</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1353,22 +1353,22 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571504</v>
+        <v>571488</v>
       </c>
       <c r="R8" t="n">
-        <v>7050910</v>
+        <v>7050864</v>
       </c>
       <c r="S8" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 13877-2025 artfynd.xlsx
+++ b/artfynd/A 13877-2025 artfynd.xlsx
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123871751</v>
+        <v>123872155</v>
       </c>
       <c r="B6" t="n">
         <v>57529</v>
@@ -1119,22 +1119,22 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Prästback, Prästback, Ång</t>
+          <t>Älggårdsberget, Älggårdsberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>571473</v>
+        <v>571504</v>
       </c>
       <c r="R6" t="n">
-        <v>7050855</v>
+        <v>7050910</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1200,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123872155</v>
+        <v>123871902</v>
       </c>
       <c r="B7" t="n">
         <v>57529</v>
@@ -1236,22 +1236,22 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Älggårdsberget, Älggårdsberget, Ång</t>
+          <t>Prästback, Prästback, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>571504</v>
+        <v>571488</v>
       </c>
       <c r="R7" t="n">
-        <v>7050910</v>
+        <v>7050864</v>
       </c>
       <c r="S7" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1280,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:04</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1317,7 +1317,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123871902</v>
+        <v>123871751</v>
       </c>
       <c r="B8" t="n">
         <v>57529</v>
@@ -1353,7 +1353,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>571488</v>
+        <v>571473</v>
       </c>
       <c r="R8" t="n">
-        <v>7050864</v>
+        <v>7050855</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD8" t="b">
